--- a/fixtures/xlsx/path-many-sheets/input.xlsx
+++ b/fixtures/xlsx/path-many-sheets/input.xlsx
@@ -19,12 +19,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
+    <t>Sheet 1 Data</t>
+  </si>
+  <si>
     <t>Sheet 1 Header</t>
   </si>
   <si>
-    <t>Sheet 1 Data</t>
-  </si>
-  <si>
     <t>Sheet 2 Header</t>
   </si>
   <si>
@@ -37,18 +37,18 @@
     <t>Sheet 3 Data</t>
   </si>
   <si>
+    <t>Sheet 4 Header</t>
+  </si>
+  <si>
     <t>Sheet 4 Data</t>
   </si>
   <si>
-    <t>Sheet 4 Header</t>
+    <t>Sheet 5 Data</t>
   </si>
   <si>
     <t>Sheet 5 Header</t>
   </si>
   <si>
-    <t>Sheet 5 Data</t>
-  </si>
-  <si>
     <t>Sheet 6 Header</t>
   </si>
   <si>
@@ -67,17 +67,17 @@
     <t>Sheet 8 Data</t>
   </si>
   <si>
+    <t>Sheet 9 Header</t>
+  </si>
+  <si>
     <t>Sheet 9 Data</t>
   </si>
   <si>
-    <t>Sheet 9 Header</t>
+    <t>Sheet 10 Header</t>
   </si>
   <si>
     <t>Sheet 10 Data</t>
   </si>
-  <si>
-    <t>Sheet 10 Header</t>
-  </si>
 </sst>
 </file>
 
@@ -86,14 +86,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -103,14 +103,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -154,14 +154,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -171,14 +171,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -239,14 +239,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/fixtures/xlsx/path-many-sheets/input.xlsx
+++ b/fixtures/xlsx/path-many-sheets/input.xlsx
@@ -19,36 +19,36 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
+    <t>Sheet 1 Header</t>
+  </si>
+  <si>
     <t>Sheet 1 Data</t>
   </si>
   <si>
-    <t>Sheet 1 Header</t>
-  </si>
-  <si>
     <t>Sheet 2 Header</t>
   </si>
   <si>
     <t>Sheet 2 Data</t>
   </si>
   <si>
+    <t>Sheet 3 Data</t>
+  </si>
+  <si>
     <t>Sheet 3 Header</t>
   </si>
   <si>
-    <t>Sheet 3 Data</t>
-  </si>
-  <si>
     <t>Sheet 4 Header</t>
   </si>
   <si>
     <t>Sheet 4 Data</t>
   </si>
   <si>
+    <t>Sheet 5 Header</t>
+  </si>
+  <si>
     <t>Sheet 5 Data</t>
   </si>
   <si>
-    <t>Sheet 5 Header</t>
-  </si>
-  <si>
     <t>Sheet 6 Header</t>
   </si>
   <si>
@@ -67,12 +67,12 @@
     <t>Sheet 8 Data</t>
   </si>
   <si>
+    <t>Sheet 9 Data</t>
+  </si>
+  <si>
     <t>Sheet 9 Header</t>
   </si>
   <si>
-    <t>Sheet 9 Data</t>
-  </si>
-  <si>
     <t>Sheet 10 Header</t>
   </si>
   <si>
@@ -86,14 +86,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -137,14 +137,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -171,14 +171,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -239,14 +239,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>